--- a/public/sap-reporting/expansion-150-downloads/EXT-SD07-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-SD07-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R63b07a9f1e64420e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R8d3640050961464c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="Rcf5d1bcb0ea04486"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R0d56f6304a4742d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Rc53d37da05fc416d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R6e440228ec6c48fa"/>
   </x:sheets>
 </x:workbook>
 </file>
